--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57724A4C-C638-4F94-8414-429DDBD0BB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D15DE4-C20B-4AAE-8BA2-BB254FF58EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="193">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -611,6 +611,12 @@
   </si>
   <si>
     <t>at grid node - w1363994055-220</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
 </sst>
 </file>
@@ -953,6 +959,12 @@
       <c r="C4" t="s">
         <v>60</v>
       </c>
+      <c r="D4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
@@ -960,6 +972,12 @@
       </c>
       <c r="C5">
         <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">

--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D15DE4-C20B-4AAE-8BA2-BB254FF58EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEBAA8E-B562-49EB-87C2-39B3D47610DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="194">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -220,9 +220,6 @@
     <t>*</t>
   </si>
   <si>
-    <t>allregions</t>
-  </si>
-  <si>
     <t>ELC_spv*</t>
   </si>
   <si>
@@ -617,6 +614,12 @@
   </si>
   <si>
     <t>SI</t>
+  </si>
+  <si>
+    <t>DeACT replicateinregions</t>
+  </si>
+  <si>
+    <t>ev_battery</t>
   </si>
 </sst>
 </file>
@@ -957,13 +960,13 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
         <v>191</v>
-      </c>
-      <c r="E4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.45">
@@ -980,18 +983,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -999,10 +1013,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
         <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>77</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -1011,10 +1025,10 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
         <v>76</v>
-      </c>
-      <c r="I10" t="s">
-        <v>77</v>
       </c>
       <c r="J10" t="s">
         <v>21</v>
@@ -1023,10 +1037,10 @@
         <v>33</v>
       </c>
       <c r="M10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" t="s">
         <v>76</v>
-      </c>
-      <c r="N10" t="s">
-        <v>77</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -1035,10 +1049,10 @@
         <v>33</v>
       </c>
       <c r="R10" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" t="s">
         <v>76</v>
-      </c>
-      <c r="S10" t="s">
-        <v>77</v>
       </c>
       <c r="T10" t="s">
         <v>21</v>
@@ -1046,1090 +1060,1090 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
         <v>78</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
       <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" t="s">
         <v>78</v>
       </c>
-      <c r="H11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I11" t="s">
-        <v>89</v>
-      </c>
-      <c r="J11" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" t="s">
-        <v>78</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>79</v>
       </c>
-      <c r="N11" t="s">
-        <v>80</v>
-      </c>
       <c r="O11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R11" t="s">
+        <v>173</v>
+      </c>
+      <c r="S11" t="s">
         <v>174</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>175</v>
-      </c>
-      <c r="T11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
         <v>82</v>
       </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
       <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" t="s">
         <v>81</v>
       </c>
-      <c r="G12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J12" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>82</v>
       </c>
-      <c r="N12" t="s">
-        <v>83</v>
-      </c>
       <c r="O12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R12" t="s">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s">
         <v>86</v>
       </c>
-      <c r="S12" t="s">
-        <v>87</v>
-      </c>
       <c r="T12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
         <v>84</v>
       </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
         <v>93</v>
       </c>
-      <c r="I13" t="s">
-        <v>94</v>
-      </c>
       <c r="J13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M13" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" t="s">
         <v>84</v>
       </c>
-      <c r="N13" t="s">
-        <v>85</v>
-      </c>
       <c r="O13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R13" t="s">
+        <v>176</v>
+      </c>
+      <c r="S13" t="s">
         <v>177</v>
       </c>
-      <c r="S13" t="s">
-        <v>178</v>
-      </c>
       <c r="T13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" t="s">
         <v>95</v>
       </c>
-      <c r="I14" t="s">
-        <v>96</v>
-      </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M14" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" t="s">
         <v>86</v>
       </c>
-      <c r="N14" t="s">
-        <v>87</v>
-      </c>
       <c r="O14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R14" t="s">
+        <v>178</v>
+      </c>
+      <c r="S14" t="s">
         <v>179</v>
       </c>
-      <c r="S14" t="s">
-        <v>180</v>
-      </c>
       <c r="T14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="G15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s">
         <v>97</v>
       </c>
-      <c r="I15" t="s">
-        <v>98</v>
-      </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M15" t="s">
+        <v>135</v>
+      </c>
+      <c r="N15" t="s">
         <v>136</v>
       </c>
-      <c r="N15" t="s">
-        <v>137</v>
-      </c>
       <c r="O15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R15" t="s">
+        <v>180</v>
+      </c>
+      <c r="S15" t="s">
         <v>181</v>
       </c>
-      <c r="S15" t="s">
-        <v>182</v>
-      </c>
       <c r="T15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="G16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" t="s">
         <v>99</v>
       </c>
-      <c r="I16" t="s">
-        <v>100</v>
-      </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M16" t="s">
+        <v>137</v>
+      </c>
+      <c r="N16" t="s">
         <v>138</v>
       </c>
-      <c r="N16" t="s">
-        <v>139</v>
-      </c>
       <c r="O16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R16" t="s">
+        <v>182</v>
+      </c>
+      <c r="S16" t="s">
         <v>183</v>
       </c>
-      <c r="S16" t="s">
-        <v>184</v>
-      </c>
       <c r="T16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
         <v>101</v>
       </c>
-      <c r="I17" t="s">
-        <v>102</v>
-      </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M17" t="s">
+        <v>139</v>
+      </c>
+      <c r="N17" t="s">
         <v>140</v>
       </c>
-      <c r="N17" t="s">
-        <v>141</v>
-      </c>
       <c r="O17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R17" t="s">
+        <v>184</v>
+      </c>
+      <c r="S17" t="s">
         <v>185</v>
       </c>
-      <c r="S17" t="s">
-        <v>186</v>
-      </c>
       <c r="T17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" t="s">
         <v>103</v>
       </c>
-      <c r="I18" t="s">
-        <v>104</v>
-      </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s">
+        <v>141</v>
+      </c>
+      <c r="N18" t="s">
         <v>142</v>
       </c>
-      <c r="N18" t="s">
-        <v>143</v>
-      </c>
       <c r="O18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R18" t="s">
+        <v>186</v>
+      </c>
+      <c r="S18" t="s">
         <v>187</v>
       </c>
-      <c r="S18" t="s">
-        <v>188</v>
-      </c>
       <c r="T18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" t="s">
         <v>105</v>
       </c>
-      <c r="I19" t="s">
-        <v>106</v>
-      </c>
       <c r="J19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M19" t="s">
+        <v>116</v>
+      </c>
+      <c r="N19" t="s">
         <v>117</v>
       </c>
-      <c r="N19" t="s">
-        <v>118</v>
-      </c>
       <c r="O19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R19" t="s">
+        <v>188</v>
+      </c>
+      <c r="S19" t="s">
         <v>189</v>
       </c>
-      <c r="S19" t="s">
-        <v>190</v>
-      </c>
       <c r="T19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20" t="s">
         <v>107</v>
       </c>
-      <c r="I20" t="s">
-        <v>108</v>
-      </c>
       <c r="J20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M20" t="s">
+        <v>143</v>
+      </c>
+      <c r="N20" t="s">
         <v>144</v>
       </c>
-      <c r="N20" t="s">
-        <v>145</v>
-      </c>
       <c r="O20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R20" t="s">
+        <v>83</v>
+      </c>
+      <c r="S20" t="s">
         <v>84</v>
       </c>
-      <c r="S20" t="s">
-        <v>85</v>
-      </c>
       <c r="T20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" t="s">
         <v>109</v>
       </c>
-      <c r="I21" t="s">
-        <v>110</v>
-      </c>
       <c r="J21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M21" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" t="s">
         <v>146</v>
       </c>
-      <c r="N21" t="s">
-        <v>147</v>
-      </c>
       <c r="O21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" t="s">
         <v>111</v>
       </c>
-      <c r="I22" t="s">
-        <v>112</v>
-      </c>
       <c r="J22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M22" t="s">
+        <v>147</v>
+      </c>
+      <c r="N22" t="s">
         <v>148</v>
       </c>
-      <c r="N22" t="s">
-        <v>149</v>
-      </c>
       <c r="O22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s">
         <v>113</v>
       </c>
-      <c r="I23" t="s">
-        <v>114</v>
-      </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M23" t="s">
+        <v>149</v>
+      </c>
+      <c r="N23" t="s">
         <v>150</v>
       </c>
-      <c r="N23" t="s">
-        <v>151</v>
-      </c>
       <c r="O23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" t="s">
         <v>115</v>
       </c>
-      <c r="I24" t="s">
-        <v>116</v>
-      </c>
       <c r="J24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M24" t="s">
+        <v>151</v>
+      </c>
+      <c r="N24" t="s">
         <v>152</v>
       </c>
-      <c r="N24" t="s">
-        <v>153</v>
-      </c>
       <c r="O24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" t="s">
         <v>117</v>
       </c>
-      <c r="I25" t="s">
-        <v>118</v>
-      </c>
       <c r="J25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M25" t="s">
+        <v>153</v>
+      </c>
+      <c r="N25" t="s">
         <v>154</v>
       </c>
-      <c r="N25" t="s">
-        <v>155</v>
-      </c>
       <c r="O25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" t="s">
         <v>119</v>
       </c>
-      <c r="I26" t="s">
-        <v>120</v>
-      </c>
       <c r="J26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M26" t="s">
+        <v>155</v>
+      </c>
+      <c r="N26" t="s">
         <v>156</v>
       </c>
-      <c r="N26" t="s">
-        <v>157</v>
-      </c>
       <c r="O26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
+        <v>120</v>
+      </c>
+      <c r="I27" t="s">
         <v>121</v>
       </c>
-      <c r="I27" t="s">
-        <v>122</v>
-      </c>
       <c r="J27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M27" t="s">
+        <v>157</v>
+      </c>
+      <c r="N27" t="s">
         <v>158</v>
       </c>
-      <c r="N27" t="s">
-        <v>159</v>
-      </c>
       <c r="O27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s">
+        <v>122</v>
+      </c>
+      <c r="I28" t="s">
         <v>123</v>
       </c>
-      <c r="I28" t="s">
-        <v>124</v>
-      </c>
       <c r="J28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M28" t="s">
+        <v>159</v>
+      </c>
+      <c r="N28" t="s">
         <v>160</v>
       </c>
-      <c r="N28" t="s">
-        <v>161</v>
-      </c>
       <c r="O28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s">
+        <v>124</v>
+      </c>
+      <c r="I29" t="s">
         <v>125</v>
       </c>
-      <c r="I29" t="s">
-        <v>126</v>
-      </c>
       <c r="J29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M29" t="s">
+        <v>161</v>
+      </c>
+      <c r="N29" t="s">
         <v>162</v>
       </c>
-      <c r="N29" t="s">
-        <v>163</v>
-      </c>
       <c r="O29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s">
+        <v>126</v>
+      </c>
+      <c r="I30" t="s">
         <v>127</v>
       </c>
-      <c r="I30" t="s">
-        <v>128</v>
-      </c>
       <c r="J30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M30" t="s">
+        <v>163</v>
+      </c>
+      <c r="N30" t="s">
         <v>164</v>
       </c>
-      <c r="N30" t="s">
-        <v>165</v>
-      </c>
       <c r="O30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" t="s">
         <v>129</v>
       </c>
-      <c r="I31" t="s">
-        <v>130</v>
-      </c>
       <c r="J31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M31" t="s">
+        <v>165</v>
+      </c>
+      <c r="N31" t="s">
         <v>166</v>
       </c>
-      <c r="N31" t="s">
-        <v>167</v>
-      </c>
       <c r="O31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
+        <v>130</v>
+      </c>
+      <c r="I32" t="s">
         <v>131</v>
       </c>
-      <c r="I32" t="s">
-        <v>132</v>
-      </c>
       <c r="J32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M32" t="s">
+        <v>167</v>
+      </c>
+      <c r="N32" t="s">
         <v>168</v>
       </c>
-      <c r="N32" t="s">
-        <v>169</v>
-      </c>
       <c r="O32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s">
+        <v>132</v>
+      </c>
+      <c r="I33" t="s">
         <v>133</v>
       </c>
-      <c r="I33" t="s">
-        <v>134</v>
-      </c>
       <c r="J33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M33" t="s">
+        <v>169</v>
+      </c>
+      <c r="N33" t="s">
         <v>170</v>
       </c>
-      <c r="N33" t="s">
-        <v>171</v>
-      </c>
       <c r="O33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M34" t="s">
+        <v>87</v>
+      </c>
+      <c r="N34" t="s">
         <v>88</v>
       </c>
-      <c r="N34" t="s">
-        <v>89</v>
-      </c>
       <c r="O34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M35" t="s">
+        <v>90</v>
+      </c>
+      <c r="N35" t="s">
         <v>91</v>
       </c>
-      <c r="N35" t="s">
-        <v>92</v>
-      </c>
       <c r="O35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M36" t="s">
+        <v>92</v>
+      </c>
+      <c r="N36" t="s">
         <v>93</v>
       </c>
-      <c r="N36" t="s">
-        <v>94</v>
-      </c>
       <c r="O36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M37" t="s">
+        <v>94</v>
+      </c>
+      <c r="N37" t="s">
         <v>95</v>
       </c>
-      <c r="N37" t="s">
-        <v>96</v>
-      </c>
       <c r="O37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M38" t="s">
+        <v>96</v>
+      </c>
+      <c r="N38" t="s">
         <v>97</v>
       </c>
-      <c r="N38" t="s">
-        <v>98</v>
-      </c>
       <c r="O38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M39" t="s">
+        <v>98</v>
+      </c>
+      <c r="N39" t="s">
         <v>99</v>
       </c>
-      <c r="N39" t="s">
-        <v>100</v>
-      </c>
       <c r="O39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M40" t="s">
+        <v>100</v>
+      </c>
+      <c r="N40" t="s">
         <v>101</v>
       </c>
-      <c r="N40" t="s">
-        <v>102</v>
-      </c>
       <c r="O40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M41" t="s">
+        <v>102</v>
+      </c>
+      <c r="N41" t="s">
         <v>103</v>
       </c>
-      <c r="N41" t="s">
-        <v>104</v>
-      </c>
       <c r="O41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M42" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" t="s">
         <v>105</v>
       </c>
-      <c r="N42" t="s">
-        <v>106</v>
-      </c>
       <c r="O42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M43" t="s">
+        <v>106</v>
+      </c>
+      <c r="N43" t="s">
         <v>107</v>
       </c>
-      <c r="N43" t="s">
-        <v>108</v>
-      </c>
       <c r="O43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M44" t="s">
+        <v>108</v>
+      </c>
+      <c r="N44" t="s">
         <v>109</v>
       </c>
-      <c r="N44" t="s">
-        <v>110</v>
-      </c>
       <c r="O44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M45" t="s">
+        <v>110</v>
+      </c>
+      <c r="N45" t="s">
         <v>111</v>
       </c>
-      <c r="N45" t="s">
-        <v>112</v>
-      </c>
       <c r="O45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M46" t="s">
+        <v>112</v>
+      </c>
+      <c r="N46" t="s">
         <v>113</v>
       </c>
-      <c r="N46" t="s">
-        <v>114</v>
-      </c>
       <c r="O46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M47" t="s">
+        <v>114</v>
+      </c>
+      <c r="N47" t="s">
         <v>115</v>
       </c>
-      <c r="N47" t="s">
-        <v>116</v>
-      </c>
       <c r="O47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M48" t="s">
+        <v>118</v>
+      </c>
+      <c r="N48" t="s">
         <v>119</v>
       </c>
-      <c r="N48" t="s">
-        <v>120</v>
-      </c>
       <c r="O48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M49" t="s">
+        <v>120</v>
+      </c>
+      <c r="N49" t="s">
         <v>121</v>
       </c>
-      <c r="N49" t="s">
-        <v>122</v>
-      </c>
       <c r="O49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M50" t="s">
+        <v>122</v>
+      </c>
+      <c r="N50" t="s">
         <v>123</v>
       </c>
-      <c r="N50" t="s">
-        <v>124</v>
-      </c>
       <c r="O50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M51" t="s">
+        <v>124</v>
+      </c>
+      <c r="N51" t="s">
         <v>125</v>
       </c>
-      <c r="N51" t="s">
-        <v>126</v>
-      </c>
       <c r="O51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M52" t="s">
+        <v>126</v>
+      </c>
+      <c r="N52" t="s">
         <v>127</v>
       </c>
-      <c r="N52" t="s">
-        <v>128</v>
-      </c>
       <c r="O52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M53" t="s">
+        <v>128</v>
+      </c>
+      <c r="N53" t="s">
         <v>129</v>
       </c>
-      <c r="N53" t="s">
-        <v>130</v>
-      </c>
       <c r="O53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M54" t="s">
+        <v>130</v>
+      </c>
+      <c r="N54" t="s">
         <v>131</v>
       </c>
-      <c r="N54" t="s">
-        <v>132</v>
-      </c>
       <c r="O54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M55" t="s">
+        <v>132</v>
+      </c>
+      <c r="N55" t="s">
         <v>133</v>
       </c>
-      <c r="N55" t="s">
-        <v>134</v>
-      </c>
       <c r="O55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M56" t="s">
+        <v>171</v>
+      </c>
+      <c r="N56" t="s">
         <v>172</v>
       </c>
-      <c r="N56" t="s">
-        <v>173</v>
-      </c>
       <c r="O56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2908,7 +2922,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="1">
         <v>8.76</v>
@@ -3457,7 +3471,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
         <v>24</v>
@@ -3468,7 +3482,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -3479,7 +3493,7 @@
         <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
         <v>24</v>
@@ -3490,7 +3504,7 @@
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -3501,7 +3515,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -3520,38 +3534,38 @@
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F49" t="s">
         <v>67</v>
-      </c>
-      <c r="F49" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" t="s">
         <v>70</v>
-      </c>
-      <c r="F50" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
